--- a/cls.var_AMR_ville_C3G_R.xlsx
+++ b/cls.var_AMR_ville_C3G_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t xml:space="preserve">log_UGB_density_livestock_tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cluster_4</t>
   </si>
   <si>
     <t xml:space="preserve">log_UGB_density_porcs</t>
@@ -590,28 +587,28 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
@@ -619,7 +616,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -627,7 +624,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
@@ -635,7 +632,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
@@ -643,7 +640,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -651,7 +648,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
@@ -659,7 +656,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -667,7 +664,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
@@ -675,7 +672,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
@@ -683,7 +680,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
@@ -691,7 +688,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
@@ -699,7 +696,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
@@ -707,7 +704,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>3</v>
@@ -715,7 +712,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -723,7 +720,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
